--- a/informes/planes.xlsx
+++ b/informes/planes.xlsx
@@ -229,7 +229,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="848511534" name="Picture">
+        <xdr:cNvPr id="1356934257" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
@@ -359,7 +359,7 @@
       <c r="N3" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">miércoles 27 mayo </t>
+            <t xml:space="preserve">domingo 31 mayo </t>
           </r>
         </is>
       </c>
@@ -648,7 +648,7 @@
       <c r="G13" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">15/1/23, 0:00</t>
+            <t xml:space="preserve">15/01/23 0:00</t>
           </r>
         </is>
       </c>
@@ -659,7 +659,7 @@
       <c r="L13" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">15/2/23, 0:00</t>
+            <t xml:space="preserve">15/02/23 0:00</t>
           </r>
         </is>
       </c>
@@ -724,7 +724,7 @@
       <c r="G15" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">10/2/23, 0:00</t>
+            <t xml:space="preserve">10/02/23 0:00</t>
           </r>
         </is>
       </c>
@@ -735,7 +735,7 @@
       <c r="L15" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">10/5/23, 0:00</t>
+            <t xml:space="preserve">10/05/23 0:00</t>
           </r>
         </is>
       </c>
@@ -800,7 +800,7 @@
       <c r="G17" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">5/3/23, 0:00</t>
+            <t xml:space="preserve">5/03/23 0:00</t>
           </r>
         </is>
       </c>
@@ -811,7 +811,7 @@
       <c r="L17" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">5/4/23, 0:00</t>
+            <t xml:space="preserve">5/04/23 0:00</t>
           </r>
         </is>
       </c>
@@ -876,7 +876,7 @@
       <c r="G19" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1/4/23, 0:00</t>
+            <t xml:space="preserve">1/04/23 0:00</t>
           </r>
         </is>
       </c>
@@ -887,7 +887,7 @@
       <c r="L19" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1/4/24, 0:00</t>
+            <t xml:space="preserve">1/04/24 0:00</t>
           </r>
         </is>
       </c>
@@ -945,14 +945,14 @@
       <c r="F21" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">90.0</t>
+            <t xml:space="preserve">100.0</t>
           </r>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">20/5/23, 0:00</t>
+            <t xml:space="preserve">20/05/23 0:00</t>
           </r>
         </is>
       </c>
@@ -963,7 +963,7 @@
       <c r="L21" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">20/11/23, 0:00</t>
+            <t xml:space="preserve">20/11/23 0:00</t>
           </r>
         </is>
       </c>
@@ -977,7 +977,7 @@
       <c r="T21" s="1" t="inlineStr"/>
       <c r="U21" s="1" t="inlineStr"/>
     </row>
-    <row r="22" customHeight="1" ht="521">
+    <row r="22" customHeight="1" ht="5">
       <c r="A22" s="1" t="inlineStr"/>
       <c r="B22" s="1" t="inlineStr"/>
       <c r="C22" s="1" t="inlineStr"/>
@@ -1002,52 +1002,58 @@
     </row>
     <row r="23" customHeight="1" ht="20">
       <c r="A23" s="1" t="inlineStr"/>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr"/>
-      <c r="D23" s="1" t="inlineStr"/>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr"/>
-      <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr"/>
-      <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pagina:</t>
-          </r>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">1</t>
-          </r>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="1" t="inlineStr"/>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">/</t>
-          </r>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">1</t>
-          </r>
-        </is>
-      </c>
-      <c r="R23" s="5" t="inlineStr"/>
-      <c r="S23" s="5" t="inlineStr"/>
-      <c r="T23" s="5" t="inlineStr"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">8</t>
+          </r>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Plan mensual básico</t>
+          </r>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">30.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">10/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr"/>
+      <c r="K23" s="8" t="inlineStr"/>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">10/02/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr"/>
+      <c r="N23" s="8" t="inlineStr"/>
+      <c r="O23" s="8" t="inlineStr"/>
+      <c r="P23" s="8" t="inlineStr"/>
+      <c r="Q23" s="8" t="inlineStr"/>
+      <c r="R23" s="8" t="inlineStr"/>
+      <c r="S23" s="1" t="inlineStr"/>
+      <c r="T23" s="1" t="inlineStr"/>
       <c r="U23" s="1" t="inlineStr"/>
     </row>
-    <row r="24" customHeight="1" ht="10">
+    <row r="24" customHeight="1" ht="5">
       <c r="A24" s="1" t="inlineStr"/>
       <c r="B24" s="1" t="inlineStr"/>
       <c r="C24" s="1" t="inlineStr"/>
@@ -1060,38 +1066,716 @@
       <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr"/>
+      <c r="M24" s="1" t="inlineStr"/>
+      <c r="N24" s="1" t="inlineStr"/>
       <c r="O24" s="1" t="inlineStr"/>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
-      <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="5" t="inlineStr"/>
-      <c r="T24" s="5" t="inlineStr"/>
+      <c r="P24" s="1" t="inlineStr"/>
+      <c r="Q24" s="1" t="inlineStr"/>
+      <c r="R24" s="1" t="inlineStr"/>
+      <c r="S24" s="1" t="inlineStr"/>
+      <c r="T24" s="1" t="inlineStr"/>
       <c r="U24" s="1" t="inlineStr"/>
     </row>
-    <row r="25" customHeight="1" ht="30">
+    <row r="25" customHeight="1" ht="20">
       <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr"/>
-      <c r="D25" s="1" t="inlineStr"/>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr"/>
-      <c r="G25" s="1" t="inlineStr"/>
-      <c r="H25" s="1" t="inlineStr"/>
-      <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr"/>
-      <c r="L25" s="1" t="inlineStr"/>
-      <c r="M25" s="1" t="inlineStr"/>
-      <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="1" t="inlineStr"/>
-      <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr"/>
-      <c r="R25" s="1" t="inlineStr"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">9</t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Plan trimestral premium</t>
+          </r>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="8" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">80.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">14/02/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr"/>
+      <c r="K25" s="8" t="inlineStr"/>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">14/05/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr"/>
+      <c r="N25" s="8" t="inlineStr"/>
+      <c r="O25" s="8" t="inlineStr"/>
+      <c r="P25" s="8" t="inlineStr"/>
+      <c r="Q25" s="8" t="inlineStr"/>
+      <c r="R25" s="8" t="inlineStr"/>
       <c r="S25" s="1" t="inlineStr"/>
       <c r="T25" s="1" t="inlineStr"/>
       <c r="U25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26" customHeight="1" ht="5">
+      <c r="A26" s="1" t="inlineStr"/>
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr"/>
+      <c r="D26" s="1" t="inlineStr"/>
+      <c r="E26" s="1" t="inlineStr"/>
+      <c r="F26" s="1" t="inlineStr"/>
+      <c r="G26" s="1" t="inlineStr"/>
+      <c r="H26" s="1" t="inlineStr"/>
+      <c r="I26" s="1" t="inlineStr"/>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
+      <c r="L26" s="1" t="inlineStr"/>
+      <c r="M26" s="1" t="inlineStr"/>
+      <c r="N26" s="1" t="inlineStr"/>
+      <c r="O26" s="1" t="inlineStr"/>
+      <c r="P26" s="1" t="inlineStr"/>
+      <c r="Q26" s="1" t="inlineStr"/>
+      <c r="R26" s="1" t="inlineStr"/>
+      <c r="S26" s="1" t="inlineStr"/>
+      <c r="T26" s="1" t="inlineStr"/>
+      <c r="U26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27" customHeight="1" ht="20">
+      <c r="A27" s="1" t="inlineStr"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">10</t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Plan anual</t>
+          </r>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">150.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr"/>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/25 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr"/>
+      <c r="N27" s="8" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr"/>
+      <c r="P27" s="8" t="inlineStr"/>
+      <c r="Q27" s="8" t="inlineStr"/>
+      <c r="R27" s="8" t="inlineStr"/>
+      <c r="S27" s="1" t="inlineStr"/>
+      <c r="T27" s="1" t="inlineStr"/>
+      <c r="U27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28" customHeight="1" ht="5">
+      <c r="A28" s="1" t="inlineStr"/>
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr"/>
+      <c r="D28" s="1" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr"/>
+      <c r="F28" s="1" t="inlineStr"/>
+      <c r="G28" s="1" t="inlineStr"/>
+      <c r="H28" s="1" t="inlineStr"/>
+      <c r="I28" s="1" t="inlineStr"/>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
+      <c r="L28" s="1" t="inlineStr"/>
+      <c r="M28" s="1" t="inlineStr"/>
+      <c r="N28" s="1" t="inlineStr"/>
+      <c r="O28" s="1" t="inlineStr"/>
+      <c r="P28" s="1" t="inlineStr"/>
+      <c r="Q28" s="1" t="inlineStr"/>
+      <c r="R28" s="1" t="inlineStr"/>
+      <c r="S28" s="1" t="inlineStr"/>
+      <c r="T28" s="1" t="inlineStr"/>
+      <c r="U28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29" customHeight="1" ht="20">
+      <c r="A29" s="1" t="inlineStr"/>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11</t>
+          </r>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Plan mensual básico</t>
+          </r>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">30.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">10/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr"/>
+      <c r="K29" s="8" t="inlineStr"/>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">10/02/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr"/>
+      <c r="N29" s="8" t="inlineStr"/>
+      <c r="O29" s="8" t="inlineStr"/>
+      <c r="P29" s="8" t="inlineStr"/>
+      <c r="Q29" s="8" t="inlineStr"/>
+      <c r="R29" s="8" t="inlineStr"/>
+      <c r="S29" s="1" t="inlineStr"/>
+      <c r="T29" s="1" t="inlineStr"/>
+      <c r="U29" s="1" t="inlineStr"/>
+    </row>
+    <row r="30" customHeight="1" ht="5">
+      <c r="A30" s="1" t="inlineStr"/>
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" s="1" t="inlineStr"/>
+      <c r="D30" s="1" t="inlineStr"/>
+      <c r="E30" s="1" t="inlineStr"/>
+      <c r="F30" s="1" t="inlineStr"/>
+      <c r="G30" s="1" t="inlineStr"/>
+      <c r="H30" s="1" t="inlineStr"/>
+      <c r="I30" s="1" t="inlineStr"/>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
+      <c r="L30" s="1" t="inlineStr"/>
+      <c r="M30" s="1" t="inlineStr"/>
+      <c r="N30" s="1" t="inlineStr"/>
+      <c r="O30" s="1" t="inlineStr"/>
+      <c r="P30" s="1" t="inlineStr"/>
+      <c r="Q30" s="1" t="inlineStr"/>
+      <c r="R30" s="1" t="inlineStr"/>
+      <c r="S30" s="1" t="inlineStr"/>
+      <c r="T30" s="1" t="inlineStr"/>
+      <c r="U30" s="1" t="inlineStr"/>
+    </row>
+    <row r="31" customHeight="1" ht="20">
+      <c r="A31" s="1" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">12</t>
+          </r>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Plan trimestral premium</t>
+          </r>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="8" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">80.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">14/02/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
+      <c r="J31" s="8" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr"/>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">14/05/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr"/>
+      <c r="N31" s="8" t="inlineStr"/>
+      <c r="O31" s="8" t="inlineStr"/>
+      <c r="P31" s="8" t="inlineStr"/>
+      <c r="Q31" s="8" t="inlineStr"/>
+      <c r="R31" s="8" t="inlineStr"/>
+      <c r="S31" s="1" t="inlineStr"/>
+      <c r="T31" s="1" t="inlineStr"/>
+      <c r="U31" s="1" t="inlineStr"/>
+    </row>
+    <row r="32" customHeight="1" ht="5">
+      <c r="A32" s="1" t="inlineStr"/>
+      <c r="B32" s="1" t="inlineStr"/>
+      <c r="C32" s="1" t="inlineStr"/>
+      <c r="D32" s="1" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr"/>
+      <c r="F32" s="1" t="inlineStr"/>
+      <c r="G32" s="1" t="inlineStr"/>
+      <c r="H32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr"/>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
+      <c r="L32" s="1" t="inlineStr"/>
+      <c r="M32" s="1" t="inlineStr"/>
+      <c r="N32" s="1" t="inlineStr"/>
+      <c r="O32" s="1" t="inlineStr"/>
+      <c r="P32" s="1" t="inlineStr"/>
+      <c r="Q32" s="1" t="inlineStr"/>
+      <c r="R32" s="1" t="inlineStr"/>
+      <c r="S32" s="1" t="inlineStr"/>
+      <c r="T32" s="1" t="inlineStr"/>
+      <c r="U32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33" customHeight="1" ht="20">
+      <c r="A33" s="1" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">13</t>
+          </r>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Plan anual</t>
+          </r>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">150.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="inlineStr"/>
+      <c r="K33" s="8" t="inlineStr"/>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/25 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr"/>
+      <c r="N33" s="8" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr"/>
+      <c r="P33" s="8" t="inlineStr"/>
+      <c r="Q33" s="8" t="inlineStr"/>
+      <c r="R33" s="8" t="inlineStr"/>
+      <c r="S33" s="1" t="inlineStr"/>
+      <c r="T33" s="1" t="inlineStr"/>
+      <c r="U33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34" customHeight="1" ht="5">
+      <c r="A34" s="1" t="inlineStr"/>
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" s="1" t="inlineStr"/>
+      <c r="D34" s="1" t="inlineStr"/>
+      <c r="E34" s="1" t="inlineStr"/>
+      <c r="F34" s="1" t="inlineStr"/>
+      <c r="G34" s="1" t="inlineStr"/>
+      <c r="H34" s="1" t="inlineStr"/>
+      <c r="I34" s="1" t="inlineStr"/>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
+      <c r="L34" s="1" t="inlineStr"/>
+      <c r="M34" s="1" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr"/>
+      <c r="O34" s="1" t="inlineStr"/>
+      <c r="P34" s="1" t="inlineStr"/>
+      <c r="Q34" s="1" t="inlineStr"/>
+      <c r="R34" s="1" t="inlineStr"/>
+      <c r="S34" s="1" t="inlineStr"/>
+      <c r="T34" s="1" t="inlineStr"/>
+      <c r="U34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35" customHeight="1" ht="20">
+      <c r="A35" s="1" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">14</t>
+          </r>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Plan mensual básico</t>
+          </r>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">30.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">10/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">10/02/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr"/>
+      <c r="N35" s="8" t="inlineStr"/>
+      <c r="O35" s="8" t="inlineStr"/>
+      <c r="P35" s="8" t="inlineStr"/>
+      <c r="Q35" s="8" t="inlineStr"/>
+      <c r="R35" s="8" t="inlineStr"/>
+      <c r="S35" s="1" t="inlineStr"/>
+      <c r="T35" s="1" t="inlineStr"/>
+      <c r="U35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36" customHeight="1" ht="5">
+      <c r="A36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr"/>
+      <c r="C36" s="1" t="inlineStr"/>
+      <c r="D36" s="1" t="inlineStr"/>
+      <c r="E36" s="1" t="inlineStr"/>
+      <c r="F36" s="1" t="inlineStr"/>
+      <c r="G36" s="1" t="inlineStr"/>
+      <c r="H36" s="1" t="inlineStr"/>
+      <c r="I36" s="1" t="inlineStr"/>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
+      <c r="L36" s="1" t="inlineStr"/>
+      <c r="M36" s="1" t="inlineStr"/>
+      <c r="N36" s="1" t="inlineStr"/>
+      <c r="O36" s="1" t="inlineStr"/>
+      <c r="P36" s="1" t="inlineStr"/>
+      <c r="Q36" s="1" t="inlineStr"/>
+      <c r="R36" s="1" t="inlineStr"/>
+      <c r="S36" s="1" t="inlineStr"/>
+      <c r="T36" s="1" t="inlineStr"/>
+      <c r="U36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37" customHeight="1" ht="20">
+      <c r="A37" s="1" t="inlineStr"/>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">15</t>
+          </r>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Plan trimestral premium</t>
+          </r>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">80.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">14/02/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
+      <c r="J37" s="8" t="inlineStr"/>
+      <c r="K37" s="8" t="inlineStr"/>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">14/05/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr"/>
+      <c r="N37" s="8" t="inlineStr"/>
+      <c r="O37" s="8" t="inlineStr"/>
+      <c r="P37" s="8" t="inlineStr"/>
+      <c r="Q37" s="8" t="inlineStr"/>
+      <c r="R37" s="8" t="inlineStr"/>
+      <c r="S37" s="1" t="inlineStr"/>
+      <c r="T37" s="1" t="inlineStr"/>
+      <c r="U37" s="1" t="inlineStr"/>
+    </row>
+    <row r="38" customHeight="1" ht="5">
+      <c r="A38" s="1" t="inlineStr"/>
+      <c r="B38" s="1" t="inlineStr"/>
+      <c r="C38" s="1" t="inlineStr"/>
+      <c r="D38" s="1" t="inlineStr"/>
+      <c r="E38" s="1" t="inlineStr"/>
+      <c r="F38" s="1" t="inlineStr"/>
+      <c r="G38" s="1" t="inlineStr"/>
+      <c r="H38" s="1" t="inlineStr"/>
+      <c r="I38" s="1" t="inlineStr"/>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
+      <c r="L38" s="1" t="inlineStr"/>
+      <c r="M38" s="1" t="inlineStr"/>
+      <c r="N38" s="1" t="inlineStr"/>
+      <c r="O38" s="1" t="inlineStr"/>
+      <c r="P38" s="1" t="inlineStr"/>
+      <c r="Q38" s="1" t="inlineStr"/>
+      <c r="R38" s="1" t="inlineStr"/>
+      <c r="S38" s="1" t="inlineStr"/>
+      <c r="T38" s="1" t="inlineStr"/>
+      <c r="U38" s="1" t="inlineStr"/>
+    </row>
+    <row r="39" customHeight="1" ht="20">
+      <c r="A39" s="1" t="inlineStr"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">16</t>
+          </r>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Plan anual</t>
+          </r>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr"/>
+      <c r="E39" s="8" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">150.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
+      <c r="J39" s="8" t="inlineStr"/>
+      <c r="K39" s="8" t="inlineStr"/>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/25 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr"/>
+      <c r="N39" s="8" t="inlineStr"/>
+      <c r="O39" s="8" t="inlineStr"/>
+      <c r="P39" s="8" t="inlineStr"/>
+      <c r="Q39" s="8" t="inlineStr"/>
+      <c r="R39" s="8" t="inlineStr"/>
+      <c r="S39" s="1" t="inlineStr"/>
+      <c r="T39" s="1" t="inlineStr"/>
+      <c r="U39" s="1" t="inlineStr"/>
+    </row>
+    <row r="40" customHeight="1" ht="296">
+      <c r="A40" s="1" t="inlineStr"/>
+      <c r="B40" s="1" t="inlineStr"/>
+      <c r="C40" s="1" t="inlineStr"/>
+      <c r="D40" s="1" t="inlineStr"/>
+      <c r="E40" s="1" t="inlineStr"/>
+      <c r="F40" s="1" t="inlineStr"/>
+      <c r="G40" s="1" t="inlineStr"/>
+      <c r="H40" s="1" t="inlineStr"/>
+      <c r="I40" s="1" t="inlineStr"/>
+      <c r="J40" s="1" t="inlineStr"/>
+      <c r="K40" s="1" t="inlineStr"/>
+      <c r="L40" s="1" t="inlineStr"/>
+      <c r="M40" s="1" t="inlineStr"/>
+      <c r="N40" s="1" t="inlineStr"/>
+      <c r="O40" s="1" t="inlineStr"/>
+      <c r="P40" s="1" t="inlineStr"/>
+      <c r="Q40" s="1" t="inlineStr"/>
+      <c r="R40" s="1" t="inlineStr"/>
+      <c r="S40" s="1" t="inlineStr"/>
+      <c r="T40" s="1" t="inlineStr"/>
+      <c r="U40" s="1" t="inlineStr"/>
+    </row>
+    <row r="41" customHeight="1" ht="20">
+      <c r="A41" s="1" t="inlineStr"/>
+      <c r="B41" s="1" t="inlineStr"/>
+      <c r="C41" s="1" t="inlineStr"/>
+      <c r="D41" s="1" t="inlineStr"/>
+      <c r="E41" s="1" t="inlineStr"/>
+      <c r="F41" s="1" t="inlineStr"/>
+      <c r="G41" s="1" t="inlineStr"/>
+      <c r="H41" s="1" t="inlineStr"/>
+      <c r="I41" s="1" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pagina:</t>
+          </r>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr"/>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1</t>
+          </r>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr"/>
+      <c r="O41" s="1" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">/</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1</t>
+          </r>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr"/>
+      <c r="S41" s="5" t="inlineStr"/>
+      <c r="T41" s="5" t="inlineStr"/>
+      <c r="U41" s="1" t="inlineStr"/>
+    </row>
+    <row r="42" customHeight="1" ht="10">
+      <c r="A42" s="1" t="inlineStr"/>
+      <c r="B42" s="1" t="inlineStr"/>
+      <c r="C42" s="1" t="inlineStr"/>
+      <c r="D42" s="1" t="inlineStr"/>
+      <c r="E42" s="1" t="inlineStr"/>
+      <c r="F42" s="1" t="inlineStr"/>
+      <c r="G42" s="1" t="inlineStr"/>
+      <c r="H42" s="1" t="inlineStr"/>
+      <c r="I42" s="1" t="inlineStr"/>
+      <c r="J42" s="1" t="inlineStr"/>
+      <c r="K42" s="1" t="inlineStr"/>
+      <c r="L42" s="1" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="1" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="5" t="inlineStr"/>
+      <c r="T42" s="5" t="inlineStr"/>
+      <c r="U42" s="1" t="inlineStr"/>
+    </row>
+    <row r="43" customHeight="1" ht="30">
+      <c r="A43" s="1" t="inlineStr"/>
+      <c r="B43" s="1" t="inlineStr"/>
+      <c r="C43" s="1" t="inlineStr"/>
+      <c r="D43" s="1" t="inlineStr"/>
+      <c r="E43" s="1" t="inlineStr"/>
+      <c r="F43" s="1" t="inlineStr"/>
+      <c r="G43" s="1" t="inlineStr"/>
+      <c r="H43" s="1" t="inlineStr"/>
+      <c r="I43" s="1" t="inlineStr"/>
+      <c r="J43" s="1" t="inlineStr"/>
+      <c r="K43" s="1" t="inlineStr"/>
+      <c r="L43" s="1" t="inlineStr"/>
+      <c r="M43" s="1" t="inlineStr"/>
+      <c r="N43" s="1" t="inlineStr"/>
+      <c r="O43" s="1" t="inlineStr"/>
+      <c r="P43" s="1" t="inlineStr"/>
+      <c r="Q43" s="1" t="inlineStr"/>
+      <c r="R43" s="1" t="inlineStr"/>
+      <c r="S43" s="1" t="inlineStr"/>
+      <c r="T43" s="1" t="inlineStr"/>
+      <c r="U43" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1120,10 +1804,37 @@
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="G21:K21"/>
     <mergeCell ref="L21:R21"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="M23:N24"/>
-    <mergeCell ref="P23:P24"/>
-    <mergeCell ref="Q23:T24"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="L23:R23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="L25:R25"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="L27:R27"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="G29:K29"/>
+    <mergeCell ref="L29:R29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="G31:K31"/>
+    <mergeCell ref="L31:R31"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="L33:R33"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="L35:R35"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="L37:R37"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="L39:R39"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="M41:N42"/>
+    <mergeCell ref="P41:P42"/>
+    <mergeCell ref="Q41:T42"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="portrait" paperSize="9"/>
